--- a/app/Plantillas.json/Entrada/eje3.xlsx
+++ b/app/Plantillas.json/Entrada/eje3.xlsx
@@ -753,13 +753,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8424A16-9570-4340-ABE7-532D292049BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEC68B-49C0-4864-8490-646DFCA76DD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB7961BD-6AB2-4AF3-A055-BED07B046BDE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AF3D894-F1D8-4766-8D74-99129FF03985}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{856CE47F-49BC-489F-988E-599C43192D45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DC3C802-FFCA-4E2A-9FC0-A6DE4595461D}"/>
 </file>
--- a/app/Plantillas.json/Entrada/eje3.xlsx
+++ b/app/Plantillas.json/Entrada/eje3.xlsx
@@ -753,13 +753,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEC68B-49C0-4864-8490-646DFCA76DD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D786EBD5-71C6-4633-BB29-014C7AD95F8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AF3D894-F1D8-4766-8D74-99129FF03985}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20FBAA6D-EC2A-4E3E-982E-2DB8CB978DA6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DC3C802-FFCA-4E2A-9FC0-A6DE4595461D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C9EE9AF-1532-4F11-8118-86D5D63FEF27}"/>
 </file>
--- a/app/Plantillas.json/Entrada/eje3.xlsx
+++ b/app/Plantillas.json/Entrada/eje3.xlsx
@@ -753,13 +753,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D786EBD5-71C6-4633-BB29-014C7AD95F8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B364D0F-B454-46F0-B8BE-493916B805C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20FBAA6D-EC2A-4E3E-982E-2DB8CB978DA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62EF0E97-6662-4695-B74F-2B23B39AE0FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C9EE9AF-1532-4F11-8118-86D5D63FEF27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB0B676E-0772-4CC7-8875-7FAC3C740E67}"/>
 </file>
--- a/app/Plantillas.json/Entrada/eje3.xlsx
+++ b/app/Plantillas.json/Entrada/eje3.xlsx
@@ -753,13 +753,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B364D0F-B454-46F0-B8BE-493916B805C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0A32A8F-494E-43FC-8B8B-B1AAA1816020}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62EF0E97-6662-4695-B74F-2B23B39AE0FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE90845-D96D-4D05-9BBF-F403B4037D5B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB0B676E-0772-4CC7-8875-7FAC3C740E67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5C4B60-1E6C-41A6-9AE5-5CABAA563BCF}"/>
 </file>